--- a/examples/MNL_modeChoice_RP.xlsx
+++ b/examples/MNL_modeChoice_RP.xlsx
@@ -13,9 +13,8 @@
     <workbookView xWindow="380" yWindow="460" windowWidth="28040" windowHeight="17040" xr2:uid="{52D9C27D-0EF6-DD41-9728-0267E68F7539}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Estimates" r:id="rId4" sheetId="2"/>
-    <sheet name="Summary" r:id="rId6" sheetId="3"/>
+    <sheet name="Estimates" sheetId="1" r:id="rId1"/>
+    <sheet name="Summary" r:id="rId5" sheetId="2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -462,312 +461,303 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2">
+        <v>1.629073210400393</v>
+      </c>
+      <c r="C2">
+        <v>0.8274352503686208</v>
+      </c>
+      <c r="D2">
+        <v>1.968822587235248</v>
+      </c>
+      <c r="E2">
+        <v>0.04897346757273602</v>
+      </c>
+      <c r="F2">
+        <v>0.8141056659851807</v>
+      </c>
+      <c r="G2">
+        <v>2.0010586812818563</v>
+      </c>
+      <c r="H2">
+        <v>0.04538606640783627</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>0.47467669268731216</v>
+      </c>
+      <c r="C3">
+        <v>1.0186722165192739</v>
+      </c>
+      <c r="D3">
+        <v>0.4659758899769021</v>
+      </c>
+      <c r="E3">
+        <v>0.6412327583488708</v>
+      </c>
+      <c r="F3">
+        <v>0.9916823152813601</v>
+      </c>
+      <c r="G3">
+        <v>0.4786580191788909</v>
+      </c>
+      <c r="H3">
+        <v>0.6321819358167948</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>0.0</v>
+      </c>
+      <c r="C4">
+        <v>NaN</v>
+      </c>
+      <c r="D4">
+        <v>NaN</v>
+      </c>
+      <c r="E4">
+        <v>NaN</v>
+      </c>
+      <c r="F4">
+        <v>NaN</v>
+      </c>
+      <c r="G4">
+        <v>NaN</v>
+      </c>
+      <c r="H4">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>0.9445331155245272</v>
+      </c>
+      <c r="C5">
+        <v>0.8035506396250885</v>
+      </c>
+      <c r="D5">
+        <v>1.1754493978938485</v>
+      </c>
+      <c r="E5">
+        <v>0.23981497051089873</v>
+      </c>
+      <c r="F5">
+        <v>0.8016189913411198</v>
+      </c>
+      <c r="G5">
+        <v>1.1782818592462612</v>
+      </c>
+      <c r="H5">
+        <v>0.23868425741535604</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>-0.011465758091658878</v>
+      </c>
+      <c r="C6">
+        <v>0.006429850139526603</v>
+      </c>
+      <c r="D6">
+        <v>-1.7832076709182905</v>
+      </c>
+      <c r="E6">
+        <v>0.07455250424099913</v>
+      </c>
+      <c r="F6">
+        <v>0.006283431512981876</v>
+      </c>
+      <c r="G6">
+        <v>-1.8247605735767252</v>
+      </c>
+      <c r="H6">
+        <v>0.06803716791203995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>-0.03394717514203955</v>
+      </c>
+      <c r="C7">
+        <v>0.0032947072297053377</v>
+      </c>
+      <c r="D7">
+        <v>-10.303548320156999</v>
+      </c>
+      <c r="E7">
+        <v>0.0</v>
+      </c>
+      <c r="F7">
+        <v>0.003293668386120358</v>
+      </c>
+      <c r="G7">
+        <v>-10.306798123664853</v>
+      </c>
+      <c r="H7">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8">
+        <v>-0.02068498987626741</v>
+      </c>
+      <c r="C8">
+        <v>0.006598906930824765</v>
+      </c>
+      <c r="D8">
+        <v>-3.134608518214409</v>
+      </c>
+      <c r="E8">
+        <v>0.0017208359227158798</v>
+      </c>
+      <c r="F8">
+        <v>0.006571727803804811</v>
+      </c>
+      <c r="G8">
+        <v>-3.1475725248832567</v>
+      </c>
+      <c r="H8">
+        <v>0.001646322596724259</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9">
+        <v>-0.00884617192110412</v>
+      </c>
+      <c r="C9">
+        <v>0.0026240861017423835</v>
+      </c>
+      <c r="D9">
+        <v>-3.371143925205158</v>
+      </c>
+      <c r="E9">
+        <v>0.0007485673875702314</v>
+      </c>
+      <c r="F9">
+        <v>0.0025739209300067165</v>
+      </c>
+      <c r="G9">
+        <v>-3.436846803635509</v>
+      </c>
+      <c r="H9">
+        <v>0.0005885283773956473</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10">
+        <v>-0.0036460770982343705</v>
+      </c>
+      <c r="C10">
+        <v>0.001554502401701868</v>
+      </c>
+      <c r="D10">
+        <v>-2.345494670347661</v>
+      </c>
+      <c r="E10">
+        <v>0.01900185025568568</v>
+      </c>
+      <c r="F10">
+        <v>0.0015685563312734171</v>
+      </c>
+      <c r="G10">
+        <v>-2.324479539268021</v>
+      </c>
+      <c r="H10">
+        <v>0.02009980693323188</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11">
+        <v>-0.011239353997987821</v>
+      </c>
+      <c r="C11">
+        <v>0.004385983456939217</v>
+      </c>
+      <c r="D11">
+        <v>-2.5625618765628606</v>
+      </c>
+      <c r="E11">
+        <v>0.01039030713160849</v>
+      </c>
+      <c r="F11">
+        <v>0.004408607980315356</v>
+      </c>
+      <c r="G11">
+        <v>-2.549411072196047</v>
+      </c>
+      <c r="H11">
+        <v>0.010790502677975766</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2">
-        <v>1.6290732104003887</v>
-      </c>
-      <c r="C2">
-        <v>0.8274352503686307</v>
-      </c>
-      <c r="D2">
-        <v>1.9688225872352187</v>
-      </c>
-      <c r="E2">
-        <v>0.04897346757273935</v>
-      </c>
-      <c r="F2">
-        <v>0.814105665985187</v>
-      </c>
-      <c r="G2">
-        <v>2.0010586812818354</v>
-      </c>
-      <c r="H2">
-        <v>0.04538606640783849</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3">
-        <v>0.474676692687307</v>
-      </c>
-      <c r="C3">
-        <v>1.0186722165192768</v>
-      </c>
-      <c r="D3">
-        <v>0.4659758899768957</v>
-      </c>
-      <c r="E3">
-        <v>0.6412327583488753</v>
-      </c>
-      <c r="F3">
-        <v>0.9916823152813223</v>
-      </c>
-      <c r="G3">
-        <v>0.4786580191789039</v>
-      </c>
-      <c r="H3">
-        <v>0.6321819358167855</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4">
-        <v>0.0</v>
-      </c>
-      <c r="C4">
-        <v>NaN</v>
-      </c>
-      <c r="D4">
-        <v>NaN</v>
-      </c>
-      <c r="E4">
-        <v>NaN</v>
-      </c>
-      <c r="F4">
-        <v>NaN</v>
-      </c>
-      <c r="G4">
-        <v>NaN</v>
-      </c>
-      <c r="H4">
-        <v>NaN</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5">
-        <v>0.9445331155245249</v>
-      </c>
-      <c r="C5">
-        <v>0.803550639625071</v>
-      </c>
-      <c r="D5">
-        <v>1.1754493978938714</v>
-      </c>
-      <c r="E5">
-        <v>0.23981497051088962</v>
-      </c>
-      <c r="F5">
-        <v>0.8016189913410574</v>
-      </c>
-      <c r="G5">
-        <v>1.17828185924635</v>
-      </c>
-      <c r="H5">
-        <v>0.23868425741532073</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6">
-        <v>-0.01146575809165884</v>
-      </c>
-      <c r="C6">
-        <v>0.006429850139526629</v>
-      </c>
-      <c r="D6">
-        <v>-1.7832076709182771</v>
-      </c>
-      <c r="E6">
-        <v>0.07455250424100135</v>
-      </c>
-      <c r="F6">
-        <v>0.006283431512981928</v>
-      </c>
-      <c r="G6">
-        <v>-1.824760573576704</v>
-      </c>
-      <c r="H6">
-        <v>0.06803716791204306</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7">
-        <v>-0.033947175142039536</v>
-      </c>
-      <c r="C7">
-        <v>0.0032947072297053355</v>
-      </c>
-      <c r="D7">
-        <v>-10.303548320157</v>
-      </c>
-      <c r="E7">
-        <v>0.0</v>
-      </c>
-      <c r="F7">
-        <v>0.003293668386120352</v>
-      </c>
-      <c r="G7">
-        <v>-10.306798123664867</v>
-      </c>
-      <c r="H7">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8">
-        <v>-0.0206849898762674</v>
-      </c>
-      <c r="C8">
-        <v>0.006598906930824885</v>
-      </c>
-      <c r="D8">
-        <v>-3.1346085182143506</v>
-      </c>
-      <c r="E8">
-        <v>0.001720835922716324</v>
-      </c>
-      <c r="F8">
-        <v>0.006571727803804985</v>
-      </c>
-      <c r="G8">
-        <v>-3.1475725248831723</v>
-      </c>
-      <c r="H8">
-        <v>0.001646322596724703</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9">
-        <v>-0.008846171921104113</v>
-      </c>
-      <c r="C9">
-        <v>0.0026240861017424065</v>
-      </c>
-      <c r="D9">
-        <v>-3.371143925205126</v>
-      </c>
-      <c r="E9">
-        <v>0.0007485673875702314</v>
-      </c>
-      <c r="F9">
-        <v>0.0025739209300066506</v>
-      </c>
-      <c r="G9">
-        <v>-3.436846803635594</v>
-      </c>
-      <c r="H9">
-        <v>0.0005885283773956473</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10">
-        <v>-0.003646077098234375</v>
-      </c>
-      <c r="C10">
-        <v>0.0015545024017018503</v>
-      </c>
-      <c r="D10">
-        <v>-2.3454946703476907</v>
-      </c>
-      <c r="E10">
-        <v>0.019001850255684127</v>
-      </c>
-      <c r="F10">
-        <v>0.0015685563312733725</v>
-      </c>
-      <c r="G10">
-        <v>-2.3244795392680904</v>
-      </c>
-      <c r="H10">
-        <v>0.020099806933228104</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11">
-        <v>-0.01123935399798782</v>
-      </c>
-      <c r="C11">
-        <v>0.004385983456939194</v>
-      </c>
-      <c r="D11">
-        <v>-2.562561876562873</v>
-      </c>
-      <c r="E11">
-        <v>0.010390307131608045</v>
-      </c>
-      <c r="F11">
-        <v>0.004408607980315112</v>
-      </c>
-      <c r="G11">
-        <v>-2.549411072196188</v>
-      </c>
-      <c r="H11">
-        <v>0.010790502677971547</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -807,7 +797,7 @@
         <v>22</v>
       </c>
       <c r="B5">
-        <v>1.4003911018371582</v>
+        <v>0.25056004524230957</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -842,11 +832,11 @@
         <v>2113.682556431493</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
         <v>27</v>
       </c>
-      <c r="B19">
+      <c r="B10">
         <v>0.12392915222483869</v>
       </c>
     </row>
